--- a/doc/TestDoc/Test Suite/TestPlanPrincipleService.xlsx
+++ b/doc/TestDoc/Test Suite/TestPlanPrincipleService.xlsx
@@ -864,7 +864,6 @@
     <col width="8.88671875" customWidth="1" style="2" min="4" max="5"/>
     <col width="22" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="8.88671875" customWidth="1" style="2" min="7" max="7"/>
-    <col width="8.88671875" customWidth="1" style="2" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1599,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H21"/>
+  <dimension ref="A3:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1609,7 +1608,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -1756,11 +1754,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED: original TC01 only expected IN_PROGRESS/turn 1 and missed the city assignment steps. PlacementService.java:72-89</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="84" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -1786,11 +1779,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>fixed: the md flagged this row as 'looks reversed' - it is correct behaviour, the conflict reset path is real (PlacementService.java:64-70); only the setup wording was incomplete</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -1816,11 +1804,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>added: checkAndResolvePlacement returns early, PlacementService.java:53-54</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -1846,11 +1829,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: PlacementService.java:32</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -1876,11 +1854,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -1906,11 +1879,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: PlacementService.java:38</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -1936,11 +1904,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -1966,11 +1929,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added: PlacementService.java:42</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -1996,11 +1954,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -2026,11 +1979,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added: flag - untested edge path, PlacementService.java:51-54</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2050,7 +1998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H18"/>
+  <dimension ref="A3:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2060,7 +2008,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -2207,7 +2154,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -2233,7 +2179,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -2259,7 +2204,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -2285,11 +2229,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: fills the TC04 gap the md flagged</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -2315,7 +2254,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -2341,11 +2279,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: PlayerService.java:28 - no existing coverage</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -2371,11 +2304,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: PlayerService.java:31</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2395,7 +2323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A3:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2405,7 +2333,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -2552,7 +2479,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="63" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -2578,7 +2504,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="46" t="inlineStr">
@@ -2604,11 +2529,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnActionService.java:51</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
@@ -2634,11 +2554,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: idempotency branch, TurnActionService.java:47-50 - answers the md's one-action-per-turn gap</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -2664,11 +2579,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnActionService.java:56</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -2694,11 +2604,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnActionService.java:42</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -2724,11 +2629,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -2754,11 +2654,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -2784,11 +2679,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added: CommandFactory.java:25</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -2814,11 +2704,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added: CommandFactory.java:26</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="46" t="inlineStr">
@@ -2844,11 +2729,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnActionService.java:44 - flag: confirm the exact exception type/message in GameStateContext before using this row</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="46" t="inlineStr">
@@ -2874,11 +2754,6 @@
       <c r="E23" s="46" t="n"/>
       <c r="F23" s="46" t="n"/>
       <c r="G23" s="46" t="n"/>
-      <c r="H23" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnActionService.java:76</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2898,7 +2773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H21"/>
+  <dimension ref="A3:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2908,7 +2783,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -3055,7 +2929,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -3081,11 +2954,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>added: answers the md's 'reset every city' suggestion, TurnService.java:62-63</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="46" t="inlineStr">
@@ -3111,11 +2979,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnService.java:44-48 - waits instead of throwing</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
@@ -3141,11 +3004,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnService.java:41</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -3171,11 +3029,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -3201,11 +3054,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnService.java:55</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -3231,11 +3079,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnService.java:57-59</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -3261,11 +3104,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -3291,11 +3129,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added: flag: confirm the exception type in GameStateContext before using this row</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -3321,11 +3154,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added: TurnService.java:70 - no existing coverage</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3355,8 +3183,6 @@
     <col width="8.21875" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="13.21875" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
     <col width="34.44140625" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
-    <col width="8.88671875" customWidth="1" style="2" min="8" max="8"/>
-    <col width="8.88671875" customWidth="1" style="2" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3462,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H41"/>
+  <dimension ref="A3:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3472,7 +3298,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="21" customHeight="1">
@@ -3628,7 +3453,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="24.6" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -3654,7 +3478,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="24.6" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -3680,7 +3503,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15" ht="24.6" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -3706,7 +3528,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="n"/>
     </row>
     <row r="16" ht="24.6" customHeight="1">
       <c r="A16" s="46" t="inlineStr">
@@ -3732,7 +3553,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="n"/>
     </row>
     <row r="17" ht="49.2" customHeight="1">
       <c r="A17" s="46" t="inlineStr">
@@ -3758,7 +3578,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="n"/>
     </row>
     <row r="18" ht="49.2" customHeight="1">
       <c r="A18" s="46" t="inlineStr">
@@ -3784,7 +3603,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="n"/>
     </row>
     <row r="19" ht="24.6" customHeight="1">
       <c r="A19" s="46" t="inlineStr">
@@ -3810,7 +3628,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="n"/>
     </row>
     <row r="20" ht="49.2" customHeight="1">
       <c r="A20" s="46" t="inlineStr">
@@ -3836,7 +3653,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="n"/>
     </row>
     <row r="21" ht="49.2" customHeight="1">
       <c r="A21" s="46" t="inlineStr">
@@ -3862,7 +3678,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="n"/>
     </row>
     <row r="22" ht="49.2" customHeight="1">
       <c r="A22" s="46" t="inlineStr">
@@ -3888,7 +3703,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="n"/>
     </row>
     <row r="23" ht="49.2" customHeight="1">
       <c r="A23" s="46" t="inlineStr">
@@ -3914,7 +3728,6 @@
       <c r="E23" s="46" t="n"/>
       <c r="F23" s="46" t="n"/>
       <c r="G23" s="46" t="n"/>
-      <c r="H23" s="48" t="n"/>
     </row>
     <row r="24" ht="73.8" customHeight="1">
       <c r="A24" s="46" t="inlineStr">
@@ -3940,7 +3753,6 @@
       <c r="E24" s="46" t="n"/>
       <c r="F24" s="46" t="n"/>
       <c r="G24" s="46" t="n"/>
-      <c r="H24" s="48" t="n"/>
     </row>
     <row r="25" ht="24.6" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
@@ -3966,11 +3778,6 @@
       <c r="E25" s="46" t="n"/>
       <c r="F25" s="46" t="n"/>
       <c r="G25" s="46" t="n"/>
-      <c r="H25" s="48" t="inlineStr">
-        <is>
-          <t>fixed: 'verity' -&gt; 'verify'</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="24.6" customHeight="1">
       <c r="A26" s="46" t="inlineStr">
@@ -3996,7 +3803,6 @@
       <c r="E26" s="46" t="n"/>
       <c r="F26" s="46" t="n"/>
       <c r="G26" s="46" t="n"/>
-      <c r="H26" s="48" t="n"/>
     </row>
     <row r="27" ht="24.6" customHeight="1">
       <c r="A27" s="46" t="inlineStr">
@@ -4022,11 +3828,6 @@
       <c r="E27" s="46" t="n"/>
       <c r="F27" s="46" t="n"/>
       <c r="G27" s="46" t="n"/>
-      <c r="H27" s="48" t="inlineStr">
-        <is>
-          <t>fixed: sheet had a second row numbered TC15; renumbered to TC16</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="123" customHeight="1">
       <c r="A28" s="46" t="inlineStr">
@@ -4052,7 +3853,6 @@
       <c r="E28" s="46" t="n"/>
       <c r="F28" s="46" t="n"/>
       <c r="G28" s="46" t="n"/>
-      <c r="H28" s="48" t="n"/>
     </row>
     <row r="29" ht="98.40000000000001" customHeight="1">
       <c r="A29" s="46" t="inlineStr">
@@ -4078,11 +3878,6 @@
       <c r="E29" s="46" t="n"/>
       <c r="F29" s="46" t="n"/>
       <c r="G29" s="46" t="n"/>
-      <c r="H29" s="48" t="inlineStr">
-        <is>
-          <t>renumbered from TC17</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="98.40000000000001" customHeight="1">
       <c r="A30" s="46" t="inlineStr">
@@ -4108,7 +3903,6 @@
       <c r="E30" s="46" t="n"/>
       <c r="F30" s="46" t="n"/>
       <c r="G30" s="46" t="n"/>
-      <c r="H30" s="48" t="n"/>
     </row>
     <row r="31" ht="98.40000000000001" customHeight="1">
       <c r="A31" s="46" t="inlineStr">
@@ -4134,11 +3928,6 @@
       <c r="E31" s="46" t="n"/>
       <c r="F31" s="46" t="n"/>
       <c r="G31" s="46" t="n"/>
-      <c r="H31" s="48" t="inlineStr">
-        <is>
-          <t>fixed: sheet had no Expected Result; findByOwner uses findByOwner_IdAndStatus(2, TRAVELING) and both armies belong to Player1</t>
-        </is>
-      </c>
     </row>
     <row r="32" ht="49.2" customHeight="1">
       <c r="A32" s="46" t="inlineStr">
@@ -4164,7 +3953,6 @@
       <c r="E32" s="46" t="n"/>
       <c r="F32" s="46" t="n"/>
       <c r="G32" s="46" t="n"/>
-      <c r="H32" s="48" t="n"/>
     </row>
     <row r="33" ht="49.2" customHeight="1">
       <c r="A33" s="46" t="inlineStr">
@@ -4190,7 +3978,6 @@
       <c r="E33" s="46" t="n"/>
       <c r="F33" s="46" t="n"/>
       <c r="G33" s="46" t="n"/>
-      <c r="H33" s="48" t="n"/>
     </row>
     <row r="34" ht="24.6" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
@@ -4216,11 +4003,6 @@
       <c r="E34" s="46" t="n"/>
       <c r="F34" s="46" t="n"/>
       <c r="G34" s="46" t="n"/>
-      <c r="H34" s="48" t="inlineStr">
-        <is>
-          <t>added: MARCH_FOOD_PER_SOLDIER = 1.25, ArmyService.java:27,55</t>
-        </is>
-      </c>
     </row>
     <row r="35" ht="24.6" customHeight="1">
       <c r="A35" s="46" t="inlineStr">
@@ -4246,11 +4028,6 @@
       <c r="E35" s="46" t="n"/>
       <c r="F35" s="46" t="n"/>
       <c r="G35" s="46" t="n"/>
-      <c r="H35" s="48" t="inlineStr">
-        <is>
-          <t>added: ArmyService.java:64</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="46" t="inlineStr">
@@ -4276,11 +4053,6 @@
       <c r="E36" s="46" t="n"/>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="46" t="n"/>
-      <c r="H36" s="48" t="inlineStr">
-        <is>
-          <t>added: ArmyService.java:65</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="46" t="inlineStr">
@@ -4306,11 +4078,6 @@
       <c r="E37" s="46" t="n"/>
       <c r="F37" s="46" t="n"/>
       <c r="G37" s="46" t="n"/>
-      <c r="H37" s="48" t="inlineStr">
-        <is>
-          <t>added: ArmyService.java:66,68</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="46" t="inlineStr">
@@ -4336,11 +4103,6 @@
       <c r="E38" s="46" t="n"/>
       <c r="F38" s="46" t="n"/>
       <c r="G38" s="46" t="n"/>
-      <c r="H38" s="48" t="inlineStr">
-        <is>
-          <t>added: ArmyService.java:68-69</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="46" t="inlineStr">
@@ -4366,11 +4128,6 @@
       <c r="E39" s="46" t="n"/>
       <c r="F39" s="46" t="n"/>
       <c r="G39" s="46" t="n"/>
-      <c r="H39" s="48" t="inlineStr">
-        <is>
-          <t>added: state itself must flip, ArmyService.java:74-77</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="46" t="inlineStr">
@@ -4396,11 +4153,6 @@
       <c r="E40" s="46" t="n"/>
       <c r="F40" s="46" t="n"/>
       <c r="G40" s="46" t="n"/>
-      <c r="H40" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
@@ -4426,11 +4178,6 @@
       <c r="E41" s="46" t="n"/>
       <c r="F41" s="46" t="n"/>
       <c r="G41" s="46" t="n"/>
-      <c r="H41" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4450,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4460,7 +4207,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -4582,7 +4328,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -4608,7 +4353,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -4634,11 +4378,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED: the old TC03 'resolveBattles(2L, 1) -&gt; Game Not Found' cannot happen - resolveBattles never loads the Game, it only queries armies, so a missing game id is silent (BattleService.java:31)</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
@@ -4664,11 +4403,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: reinforcement branch, BattleService.java:103-110</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -4694,11 +4428,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added: resolveReciprocalFieldBattles, BattleService.java:45-91</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -4724,11 +4453,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: BattleService.java:126,136-169</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -4754,11 +4478,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: Kongming survival branch, BattleService.java:139-152</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -4784,11 +4503,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added: BattleService.java:183-189</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -4814,11 +4528,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added: BattleService.java:35-37 - answers the md's 'multiple armies' gap</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -4844,11 +4553,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="46" t="inlineStr">
@@ -4874,11 +4578,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>added: BattleService.java:40-41 - needs checkWinCondition mock to set FINISHED</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4891,7 +4590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H37"/>
+  <dimension ref="A3:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4901,7 +4600,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -5023,7 +4721,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -5049,7 +4746,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="63" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -5075,11 +4771,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>verified: winter halves production, CityService.java:42</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="63" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -5105,7 +4796,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="n"/>
     </row>
     <row r="16" ht="63" customHeight="1">
       <c r="A16" s="46" t="inlineStr">
@@ -5131,7 +4821,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="n"/>
     </row>
     <row r="17" ht="63" customHeight="1">
       <c r="A17" s="46" t="inlineStr">
@@ -5157,7 +4846,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="n"/>
     </row>
     <row r="18" ht="63" customHeight="1">
       <c r="A18" s="46" t="inlineStr">
@@ -5183,7 +4871,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="n"/>
     </row>
     <row r="19" ht="63" customHeight="1">
       <c r="A19" s="46" t="inlineStr">
@@ -5209,11 +4896,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED from 1 -&gt; 3: getConnectedNetwork is a full BFS over same-player edges (CityService.java:157-176), not depth-1. Original sheet row was wrong -&gt; possible DefectID D01</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="46" t="inlineStr">
@@ -5239,7 +4921,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="46" t="inlineStr">
@@ -5265,7 +4946,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="46" t="inlineStr">
@@ -5291,11 +4971,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>fixed: 'verity' -&gt; 'verify'</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="63" customHeight="1">
       <c r="A23" s="46" t="inlineStr">
@@ -5321,7 +4996,6 @@
       <c r="E23" s="46" t="n"/>
       <c r="F23" s="46" t="n"/>
       <c r="G23" s="46" t="n"/>
-      <c r="H23" s="48" t="n"/>
     </row>
     <row r="24" ht="84" customHeight="1">
       <c r="A24" s="46" t="inlineStr">
@@ -5347,11 +5021,6 @@
       <c r="E24" s="46" t="n"/>
       <c r="F24" s="46" t="n"/>
       <c r="G24" s="46" t="n"/>
-      <c r="H24" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED: network = 3 cities, perCityCost = 10/3 = 3, remainder 1 goes to the source city -&gt; source pays 7. Original sheet listed 95/95/90, which cannot come from this code -&gt; possible DefectID D02</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="84" customHeight="1">
       <c r="A25" s="46" t="inlineStr">
@@ -5377,11 +5046,6 @@
       <c r="E25" s="46" t="n"/>
       <c r="F25" s="46" t="n"/>
       <c r="G25" s="46" t="n"/>
-      <c r="H25" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED from 'FoodTotal = 50': fair split is 25/25, then City1 absorbs City3's shortfall so City1 75-&gt;0 and City3 75-&gt;25 (debt redistribution). CityService.java:196-228 -&gt; possible DefectID D03</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="84" customHeight="1">
       <c r="A26" s="46" t="inlineStr">
@@ -5407,11 +5071,6 @@
       <c r="E26" s="46" t="n"/>
       <c r="F26" s="46" t="n"/>
       <c r="G26" s="46" t="n"/>
-      <c r="H26" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED: totalFood 150 &gt;= totalSoldiers 75 so the deficit branch never runs; perCityCost 37 + remainder 1 on the triggering City1. The original row expected all food 0 and City3 soldiers 0, which only happens when totalFood &lt; totalSoldiers -&gt; possible DefectID D04</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="46" t="inlineStr">
@@ -5437,11 +5096,6 @@
       <c r="E27" s="46" t="n"/>
       <c r="F27" s="46" t="n"/>
       <c r="G27" s="46" t="n"/>
-      <c r="H27" s="48" t="inlineStr">
-        <is>
-          <t>added: CityService.java:187</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="46" t="inlineStr">
@@ -5467,11 +5121,6 @@
       <c r="E28" s="46" t="n"/>
       <c r="F28" s="46" t="n"/>
       <c r="G28" s="46" t="n"/>
-      <c r="H28" s="48" t="inlineStr">
-        <is>
-          <t>added: CityService.java:188,191</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="46" t="inlineStr">
@@ -5497,11 +5146,6 @@
       <c r="E29" s="46" t="n"/>
       <c r="F29" s="46" t="n"/>
       <c r="G29" s="46" t="n"/>
-      <c r="H29" s="48" t="inlineStr">
-        <is>
-          <t>added: totalFood &gt;= totalSoldiers branch</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="46" t="inlineStr">
@@ -5527,11 +5171,6 @@
       <c r="E30" s="46" t="n"/>
       <c r="F30" s="46" t="n"/>
       <c r="G30" s="46" t="n"/>
-      <c r="H30" s="48" t="inlineStr">
-        <is>
-          <t>added: perCityCost 14, remainder 1 absorbed by the triggering city (CityService.java:203)</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="46" t="inlineStr">
@@ -5557,11 +5196,6 @@
       <c r="E31" s="46" t="n"/>
       <c r="F31" s="46" t="n"/>
       <c r="G31" s="46" t="n"/>
-      <c r="H31" s="48" t="inlineStr">
-        <is>
-          <t>added: negative-balance resolution, CityService.java:109-130</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
@@ -5587,11 +5221,6 @@
       <c r="E32" s="46" t="n"/>
       <c r="F32" s="46" t="n"/>
       <c r="G32" s="46" t="n"/>
-      <c r="H32" s="48" t="inlineStr">
-        <is>
-          <t>added: each network processed independently</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="46" t="inlineStr">
@@ -5617,11 +5246,6 @@
       <c r="E33" s="46" t="n"/>
       <c r="F33" s="46" t="n"/>
       <c r="G33" s="46" t="n"/>
-      <c r="H33" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED from the md's 'excess food is not fully consumed': the deficit branch sets food = 0 for EVERY city in the network (CityService.java:247); only the soldiers lost differ (totalExcess 2 offsets 2 of City2's 12 deficit)</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="46" t="inlineStr">
@@ -5647,11 +5271,6 @@
       <c r="E34" s="46" t="n"/>
       <c r="F34" s="46" t="n"/>
       <c r="G34" s="46" t="n"/>
-      <c r="H34" s="48" t="inlineStr">
-        <is>
-          <t>added: Math.round + remainder logic, CityService.java:251-263</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="46" t="inlineStr">
@@ -5677,11 +5296,6 @@
       <c r="E35" s="46" t="n"/>
       <c r="F35" s="46" t="n"/>
       <c r="G35" s="46" t="n"/>
-      <c r="H35" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="46" t="inlineStr">
@@ -5707,11 +5321,6 @@
       <c r="E36" s="46" t="n"/>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="46" t="n"/>
-      <c r="H36" s="48" t="inlineStr">
-        <is>
-          <t>added: saveAll is outside the loop, CityService.java:282</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="46" t="inlineStr">
@@ -5737,11 +5346,6 @@
       <c r="E37" s="46" t="n"/>
       <c r="F37" s="46" t="n"/>
       <c r="G37" s="46" t="n"/>
-      <c r="H37" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5754,7 +5358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H19"/>
+  <dimension ref="A3:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5764,7 +5368,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -5911,7 +5514,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -5937,7 +5539,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -5963,7 +5564,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
@@ -5989,11 +5589,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: cycle starts at turn 1, turn 0 wraps to the last slot. GameClock.java:9</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -6019,11 +5614,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -6049,11 +5639,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: flag - odd negative turns are treated as NIGHT. GameClock.java:16</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -6079,11 +5664,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: GameClock.java:20</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -6109,11 +5689,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added: answers the md's large-turn case</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6133,7 +5708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H18"/>
+  <dimension ref="A3:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6143,7 +5718,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -6290,7 +5864,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -6316,7 +5889,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -6342,7 +5914,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="46" t="inlineStr">
@@ -6368,11 +5939,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added: alive.isEmpty() ? null : alive.get(0), GameRuleService.java:40 - answers the md's 0-player edge case</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -6398,11 +5964,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -6428,11 +5989,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: GameRuleService.java:38</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -6458,11 +6014,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: flag - code has no 'already eliminated' short-circuit, so save runs every call</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6482,7 +6033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A3:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6492,7 +6043,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -6639,7 +6189,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -6665,7 +6214,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -6691,7 +6239,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="n"/>
     </row>
     <row r="15" ht="63" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -6717,11 +6264,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>CORRECTED: original row reused TC03's message. GameService only rejects non-WAITING games or blank names - there is NO duplicate-name rule, so the old expectation was a copy-paste error. GameService.java:54-56</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="46" t="inlineStr">
@@ -6747,11 +6289,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added: GameService.java:55</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -6777,11 +6314,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: MIN_PLAYERS = 2, GameService.java:26,68 - answers the md's minimum-player gap</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -6807,7 +6339,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -6833,11 +6364,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="inlineStr">
-        <is>
-          <t>added: GameService.java:66</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -6863,11 +6389,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added: GameService.java:71</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -6893,11 +6414,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added: sheet had no coverage for this method</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="46" t="inlineStr">
@@ -6923,11 +6439,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>added: GameService.java:171</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6947,7 +6458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H26"/>
+  <dimension ref="A3:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6957,7 +6468,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="3" ht="42" customHeight="1">
@@ -7104,7 +6614,6 @@
       <c r="E12" s="46" t="n"/>
       <c r="F12" s="46" t="n"/>
       <c r="G12" s="46" t="n"/>
-      <c r="H12" s="48" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="46" t="inlineStr">
@@ -7130,11 +6639,6 @@
       <c r="E13" s="46" t="n"/>
       <c r="F13" s="46" t="n"/>
       <c r="G13" s="46" t="n"/>
-      <c r="H13" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:45-46</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="46" t="inlineStr">
@@ -7160,11 +6664,6 @@
       <c r="E14" s="46" t="n"/>
       <c r="F14" s="46" t="n"/>
       <c r="G14" s="46" t="n"/>
-      <c r="H14" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:39-43</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
@@ -7190,11 +6689,6 @@
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="46" t="n"/>
       <c r="G15" s="46" t="n"/>
-      <c r="H15" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
@@ -7220,11 +6714,6 @@
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="46" t="n"/>
       <c r="G16" s="46" t="n"/>
-      <c r="H16" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="46" t="inlineStr">
@@ -7250,11 +6739,6 @@
       <c r="E17" s="46" t="n"/>
       <c r="F17" s="46" t="n"/>
       <c r="G17" s="46" t="n"/>
-      <c r="H17" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:59</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
@@ -7280,11 +6764,6 @@
       <c r="E18" s="46" t="n"/>
       <c r="F18" s="46" t="n"/>
       <c r="G18" s="46" t="n"/>
-      <c r="H18" s="48" t="inlineStr">
-        <is>
-          <t>added: usedMarshalIds filter, MarshalDraftService.java:48-51</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="46" t="inlineStr">
@@ -7310,7 +6789,6 @@
       <c r="E19" s="46" t="n"/>
       <c r="F19" s="46" t="n"/>
       <c r="G19" s="46" t="n"/>
-      <c r="H19" s="48" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="46" t="inlineStr">
@@ -7336,11 +6814,6 @@
       <c r="E20" s="46" t="n"/>
       <c r="F20" s="46" t="n"/>
       <c r="G20" s="46" t="n"/>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:70</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="46" t="inlineStr">
@@ -7366,11 +6839,6 @@
       <c r="E21" s="46" t="n"/>
       <c r="F21" s="46" t="n"/>
       <c r="G21" s="46" t="n"/>
-      <c r="H21" s="48" t="inlineStr">
-        <is>
-          <t>added: ensureCurrentDraftPlayer, MarshalDraftService.java:108-110</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="46" t="inlineStr">
@@ -7396,11 +6864,6 @@
       <c r="E22" s="46" t="n"/>
       <c r="F22" s="46" t="n"/>
       <c r="G22" s="46" t="n"/>
-      <c r="H22" s="48" t="inlineStr">
-        <is>
-          <t>added</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="46" t="inlineStr">
@@ -7426,7 +6889,6 @@
       <c r="E23" s="46" t="n"/>
       <c r="F23" s="46" t="n"/>
       <c r="G23" s="46" t="n"/>
-      <c r="H23" s="48" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="46" t="inlineStr">
@@ -7452,11 +6914,6 @@
       <c r="E24" s="46" t="n"/>
       <c r="F24" s="46" t="n"/>
       <c r="G24" s="46" t="n"/>
-      <c r="H24" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:82</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="46" t="inlineStr">
@@ -7482,11 +6939,6 @@
       <c r="E25" s="46" t="n"/>
       <c r="F25" s="46" t="n"/>
       <c r="G25" s="46" t="n"/>
-      <c r="H25" s="48" t="inlineStr">
-        <is>
-          <t>added: MarshalDraftService.java:91-96</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="46" t="inlineStr">
@@ -7512,11 +6964,6 @@
       <c r="E26" s="46" t="n"/>
       <c r="F26" s="46" t="n"/>
       <c r="G26" s="46" t="n"/>
-      <c r="H26" s="48" t="inlineStr">
-        <is>
-          <t>added: flag - candidates.isEmpty() is checked AFTER candidates.get(slot-1) is evaluated (line 82 vs 83), so the real failure is IndexOutOfBoundsException. This is a candidate DefectID D05</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
